--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>19516.45</v>
+        <v>19627.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>16.15</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1208.448916408669</v>
+        <v>1208.568349753695</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.4211015564489085</v>
+        <v>0.4210730312030253</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06191950464396286</v>
+        <v>0.06157635467980296</v>
       </c>
     </row>
     <row r="8">
@@ -720,10 +720,10 @@
         <v>19.88428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24029.14352498895</v>
+        <v>24031.51837174525</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.2312251216275987</v>
+        <v>0.2244018296973962</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>24.38571428571429</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29468.89000442283</v>
+        <v>29471.80247185081</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.5099513489606371</v>
+        <v>0.5015833919774808</v>
       </c>
     </row>
     <row r="15"/>
@@ -3877,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3968,6 +3968,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>19627.15</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.09848484848480001</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.421073031203</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>19627.15</v>
+        <v>19555.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>16.24</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1208.568349753695</v>
+        <v>1208.627935723115</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.4210730312030253</v>
+        <v>0.4208275584006986</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06157635467980296</v>
+        <v>0.06180469715698393</v>
       </c>
     </row>
     <row r="8">
@@ -720,10 +720,10 @@
         <v>19.88428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24031.51837174525</v>
+        <v>24032.70319618576</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.2244018296973962</v>
+        <v>0.2289422567543704</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>24.38571428571429</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29471.80247185081</v>
+        <v>29473.25551827653</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.5015833919774808</v>
+        <v>0.5071516863853083</v>
       </c>
     </row>
     <row r="15"/>
@@ -3877,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4001,6 +4001,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>19555.6</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.09848484848480001</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.420827558401</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>19555.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>16.18</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.09848484848484848</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>1208.627935723115</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.4208275584006986</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>90.15151515151516</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>100</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>93.10606060606059</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>19.88428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>24032.70319618576</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.2289422567543704</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>24.38571428571429</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>29473.25551827653</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.5071516863853083</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +811,17 @@
       <c r="B18" t="n">
         <v>6</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.5139281228435113</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.2333119526577105</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.2512250461377193</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,17 +834,17 @@
       <c r="B19" t="n">
         <v>7</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.2759553123533951</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.2273205201071804</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.2179114106095108</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -842,17 +857,17 @@
       <c r="B20" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.04158210140847518</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1505962565443759</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.2359175641577784</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -865,17 +880,17 @@
       <c r="B21" t="n">
         <v>7</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>-0.00047578670368148</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.1580333614610401</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.1517848882801471</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -888,21 +903,20 @@
       <c r="B22" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.01950708306457694</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.2034414253706042</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1506948051896606</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1038,16 +1052,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>9154.559999999999</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>22.68</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1057,16 +1071,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>9781.629999999999</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>23.69</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1076,16 +1090,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>10090.67</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>23.41</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1095,16 +1109,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>10248.72</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>23.24</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1114,16 +1128,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>10933.68</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>23.89</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1133,16 +1147,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>11255.08</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>24.59</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1152,16 +1166,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>10886.49</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>23.32</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1171,16 +1185,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>10619.82</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>22.55</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1190,16 +1204,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>11074.59</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>21.85</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1209,16 +1223,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>10684.32</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>21.1</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1228,16 +1242,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>10424.34</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>20.16</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1247,16 +1261,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>10701.1</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>20.69</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1266,16 +1280,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>10674.56</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>20.53</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1285,16 +1299,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>10511.67</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>19.79</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1304,16 +1318,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>10018.88</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>18.12</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1323,16 +1337,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>10967.88</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>19.9</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1342,16 +1356,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>11268.99</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>19.59</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1361,16 +1375,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>11105.53</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>18.06</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1380,16 +1394,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>11478.59</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>18.84</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1399,16 +1413,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>11883.74</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>19.02</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1418,16 +1432,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>11435.95</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>14.86</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1437,16 +1451,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>11286.06</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>14.57</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1456,16 +1470,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>11207.2</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>14.03</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1475,16 +1489,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>11392.81</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>14.26</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1494,16 +1508,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>11914.43</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>14.87</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1513,16 +1527,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>12461.1</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>15.03</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1532,16 +1546,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>13207.13</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>16.66</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1551,16 +1565,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>13822.95</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>17.35</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1570,16 +1584,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>13613.35</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>16.58</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1589,16 +1603,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>14170.16</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>17.24</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1608,16 +1622,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>14008.85</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>16.88</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1627,16 +1641,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>15475.87</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>17.85</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1646,16 +1660,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>16996.76</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>18.18</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1665,16 +1679,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>17912.92</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>18.96</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1684,16 +1698,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>18254.2</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>18.93</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1703,16 +1717,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>18329.04</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>19.01</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1722,16 +1736,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>18896.81</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>19.48</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1741,16 +1755,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>19568.02</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>19.14</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1760,16 +1774,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>20647.43</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>21.75</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1779,16 +1793,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>22326.74</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>23.15</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1798,16 +1812,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>22518.63</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>23.03</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1817,16 +1831,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>22716.73</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>23.24</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1836,16 +1850,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>20949.11</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>21.23</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1855,16 +1869,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>20870.76</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>21.32</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1874,16 +1888,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>20379.55</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>27.01</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1893,16 +1907,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>19961.4</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>26.21</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1912,16 +1926,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>18077.45</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>23.52</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1931,16 +1945,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>19091.2</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>24.82</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1950,16 +1964,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>19722.5</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>25.43</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1969,16 +1983,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>20255.15</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>25.77</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1988,16 +2002,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>20720.9</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>25.09</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2007,16 +2021,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>20380.05</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>24.61</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2026,16 +2040,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>20625.95</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>24.25</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2045,16 +2059,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>20531.15</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>24.15</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2064,16 +2078,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>20972.5</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>24.79</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2083,16 +2097,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>21381.85</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>24.44</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2102,16 +2116,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>21453.15</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>23.77</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2121,16 +2135,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>20838</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>22.79</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2140,16 +2154,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>20686.7</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>22.56</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2159,16 +2173,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>18543.9</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>20.23</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2178,16 +2192,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>20025.55</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>21.61</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2197,16 +2211,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>19802.65</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>21.19</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2216,16 +2230,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>19921.05</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>16.61</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2235,16 +2249,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>20544.15</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>16.98</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2254,16 +2268,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>20212.2</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>16.72</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2365,13 +2379,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>6428.23</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>19.84</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2379,12 +2393,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,C2)+1)/2)/COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2392,28 +2406,28 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16" t="n"/>
+      <c r="L2" s="30" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>7087.55</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>24.47</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2421,12 +2435,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,C3)+1)/2)/COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2434,28 +2448,28 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16" t="n"/>
+      <c r="L3" s="30" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>6865.65</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>22.55</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2463,12 +2477,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,C4)+1)/2)/COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2476,28 +2490,28 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16" t="n"/>
+      <c r="L4" s="30" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>7023.09</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>26.78</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2505,12 +2519,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,C5)+1)/2)/COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2518,28 +2532,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>7023.83</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>27.8</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2547,15 +2561,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,C6)+1)/2)/COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2563,28 +2577,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>7131.23</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>24.58</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2592,15 +2606,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,C7)+1)/2)/COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2608,28 +2622,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>7310.94</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>23.86</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2637,15 +2651,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,C8)+1)/2)/COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2653,28 +2667,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>7160.09</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>22.46</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2682,15 +2696,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,C9)+1)/2)/COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2698,28 +2712,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>7290.72</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>21.3</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2727,15 +2741,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,C10)+1)/2)/COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2743,28 +2757,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>7290.46</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>20.12</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2772,15 +2786,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,C11)+1)/2)/COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2788,28 +2802,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>6042.81</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>16.88</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2817,15 +2831,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,C12)+1)/2)/COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2833,28 +2847,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>6961.87</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>19.03</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2862,15 +2876,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,C13)+1)/2)/COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2878,28 +2892,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>7661.87</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>21.26</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2907,15 +2921,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,C14)+1)/2)/COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2923,28 +2937,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>8986.4</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>24.71</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2952,15 +2966,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,C15)+1)/2)/COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -2968,28 +2982,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>9148.379999999999</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>22.73</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2997,15 +3011,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,C16)+1)/2)/COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3013,28 +3027,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>10090.67</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>23.41</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3042,15 +3056,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,C17)+1)/2)/COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3058,28 +3072,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>11255.08</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>24.59</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3087,15 +3101,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,C18)+1)/2)/COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3103,25 +3117,25 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
+      <c r="K18" s="30" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>11074.59</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>21.85</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3129,15 +3143,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,C19)+1)/2)/COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3145,25 +3159,25 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
+      <c r="K19" s="30" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>10701.1</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>20.69</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3171,15 +3185,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,C20)+1)/2)/COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3187,25 +3201,25 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
+      <c r="K20" s="30" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>10018.88</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>18.12</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3213,15 +3227,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,C21)+1)/2)/COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3229,25 +3243,25 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
+      <c r="K21" s="30" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>11105.53</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>18.06</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3255,15 +3269,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,C22)+1)/2)/COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3271,25 +3285,25 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="16" t="n"/>
+      <c r="K22" s="30" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>11435.95</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>14.86</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3297,15 +3311,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,C23)+1)/2)/COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3313,25 +3327,25 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
+      <c r="K23" s="30" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>11392.81</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>14.26</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3339,15 +3353,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,C24)+1)/2)/COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3355,25 +3369,25 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>13207.13</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>16.66</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3381,15 +3395,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,C25)+1)/2)/COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3397,25 +3411,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>14170.16</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>17.24</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3423,15 +3437,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,C26)+1)/2)/COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3439,22 +3453,22 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="J26" s="30" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>16996.76</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>18.18</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3462,15 +3476,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,C27)+1)/2)/COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3478,22 +3492,22 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="J27" s="30" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>18329.04</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>19.01</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3501,15 +3515,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,C28)+1)/2)/COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3517,22 +3531,22 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="J28" s="30" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>20647.43</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>21.75</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3540,15 +3554,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,C29)+1)/2)/COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3556,22 +3570,22 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="J29" s="30" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>22716.73</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>23.24</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3579,15 +3593,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,C30)+1)/2)/COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3595,22 +3609,22 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="J30" s="30" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>20379.55</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>27.01</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3618,15 +3632,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,C31)+1)/2)/COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3634,22 +3648,22 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>19091.2</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>24.82</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3657,15 +3671,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,C32)+1)/2)/COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3673,22 +3687,22 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="J32" s="30" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>20720.9</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>25.09</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3696,15 +3710,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,C33)+1)/2)/COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3712,22 +3726,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>20531.15</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>24.15</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3735,15 +3749,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,C34)+1)/2)/COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3751,19 +3765,19 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16" t="n"/>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="I34" s="30" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>21453.15</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>23.77</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3771,15 +3785,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,C35)+1)/2)/COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3787,19 +3801,19 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="I35" s="30" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>18543.9</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>20.23</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3807,15 +3821,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,C36)+1)/2)/COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3823,19 +3837,19 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="I36" s="30" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>19921.05</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>16.61</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3843,15 +3857,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,C37)+1)/2)/COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
@@ -3859,10 +3873,10 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16" t="n"/>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="I37" s="30" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3939,30 +3953,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>19516.45</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>16.15</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.09848484848480001</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.421101556449</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -3972,30 +3986,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>19627.15</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>16.24</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.09848484848480001</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.421073031203</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4005,30 +4019,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>19555.6</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>16.18</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.09848484848480001</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.420827558401</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4148,4 +4162,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Alpha Quality Value Low Volatility 30 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4061,6 +4064,712 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY Alpha Quality Value Low-Volatility 30 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Alkem Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bajaj Auto Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Britannia Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cipla Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Coal India Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Colgate Palmolive (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Eicher Motors Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Federal Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Grasim Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hindalco Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ICICI Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ITC Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lupin Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Marico Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nestle India Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NMDC Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NTPC Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>State Bank of India</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Zydus Lifesciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4162,43 +4871,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty Alpha Quality Value Low Volatility 30 Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19555.6</v>
+        <v>19685.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>16.18</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1208.627935723115</v>
+        <v>1208.440761203192</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4208275584006986</v>
+        <v>0.4208625954653309</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06180469715698393</v>
+        <v>0.06138735420503377</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.88428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24032.70319618576</v>
+        <v>24028.98136455319</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2289422567543704</v>
+        <v>0.22064369025695</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.38571428571429</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29473.25551827653</v>
+        <v>29468.69113391213</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5071516863853083</v>
+        <v>0.4969744803998948</v>
       </c>
     </row>
     <row r="16">
@@ -3894,7 +3894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4051,6 +4051,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>19685.5</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.09848484848480001</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.420862595465</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19685.5</v>
+        <v>19505.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>16.29</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1208.440761203192</v>
+        <v>1208.513011152416</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4208625954653309</v>
+        <v>0.4207345067696391</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06138735420503377</v>
+        <v>0.06195786864931846</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.88428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24028.98136455319</v>
+        <v>24030.4180031864</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.22064369025695</v>
+        <v>0.2319879624712335</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.38571428571429</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29468.69113391213</v>
+        <v>29470.45300053107</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4969744803998948</v>
+        <v>0.5108868826340944</v>
       </c>
     </row>
     <row r="16">
@@ -3894,7 +3894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4084,6 +4084,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>19505.4</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.09848484848480001</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.42073450677</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4124,7 +4157,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19505.4</v>
+        <v>19523.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>16.14</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1208.513011152416</v>
+        <v>1208.894736842105</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4207345067696391</v>
+        <v>0.4212276599461153</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06195786864931846</v>
+        <v>0.06191950464396286</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.88428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24030.4180031864</v>
+        <v>24038.00834586466</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2319879624712335</v>
+        <v>0.2312251216275985</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.38571428571429</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29470.45300053107</v>
+        <v>29479.76165413534</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5108868826340944</v>
+        <v>0.5099513489606369</v>
       </c>
     </row>
     <row r="16">
@@ -3894,7 +3894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4117,6 +4117,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>19523.65</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.09848484848480001</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.421227659946</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4157,7 +4190,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19523.65</v>
+        <v>19275.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>16.15</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1208.894736842105</v>
+        <v>1208.479623824451</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4212276599461153</v>
+        <v>0.4205979111844893</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06191950464396286</v>
+        <v>0.06269592476489029</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.88428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24038.00834586466</v>
+        <v>24029.75412001791</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2312251216275985</v>
+        <v>0.2466636811464398</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.38571428571429</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29479.76165413534</v>
+        <v>29469.63882669055</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5099513489606369</v>
+        <v>0.5288849081952531</v>
       </c>
     </row>
     <row r="16">
@@ -3894,7 +3894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4150,6 +4150,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>19275.25</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.09848484848480001</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.420597911184</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4190,7 +4223,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19275.25</v>
+        <v>19138.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.95</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1208.479623824451</v>
+        <v>1208.979785217941</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4205979111844893</v>
+        <v>0.4216672092567468</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06269592476489029</v>
+        <v>0.06317119393556538</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.88428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24029.75412001791</v>
+        <v>24039.69947206931</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2466636811464398</v>
+        <v>0.2561140691273349</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.38571428571429</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29469.63882669055</v>
+        <v>29481.83561952892</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5288849081952531</v>
+        <v>0.5404746864001442</v>
       </c>
     </row>
     <row r="16">
@@ -3894,7 +3894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4183,6 +4183,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>19138.15</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.09848484848480001</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.421667209257</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4223,7 +4256,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>19138.15</v>
+        <v>18997.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.83</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.09848484848484848</v>
+        <v>0.1044776119402985</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1208.979785217941</v>
+        <v>1209.248886059834</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4216672092567468</v>
+        <v>0.4223928322741297</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06317119393556538</v>
+        <v>0.06365372374283895</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>90.15151515151516</v>
+        <v>89.55223880597015</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.10606060606059</v>
+        <v>92.68656716417911</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>19.88428571428571</v>
+        <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24039.69947206931</v>
+        <v>23969.04042011457</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2561140691273349</v>
+        <v>0.2617077384741291</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.38571428571429</v>
+        <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29481.83561952892</v>
+        <v>29455.57536600891</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5404746864001442</v>
+        <v>0.5505137764844958</v>
       </c>
     </row>
     <row r="16">
@@ -815,10 +815,10 @@
         <v>6</v>
       </c>
       <c r="C18" s="30" t="n">
-        <v>0.5139281228435113</v>
+        <v>0.5000925291048076</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>0.2333119526577105</v>
+        <v>0.2343413383059733</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0.2512250461377193</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.2759553123533951</v>
+        <v>0.297089752538766</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.2273205201071804</v>
+        <v>0.1619098643813</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.2179114106095108</v>
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.04158210140847518</v>
+        <v>0.04624464102179193</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.1505962565443759</v>
+        <v>0.1345450069933184</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0.2359175641577784</v>
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>-0.00047578670368148</v>
+        <v>0.00616291948557679</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>0.1580333614610401</v>
+        <v>0.1917323432218313</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>0.1517848882801471</v>
@@ -907,13 +907,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="30" t="n">
-        <v>0.01950708306457694</v>
+        <v>0.003109874850221406</v>
       </c>
       <c r="D22" s="30" t="n">
         <v>0.2034414253706042</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>0.1506948051896606</v>
+        <v>0.1426647297439754</v>
       </c>
       <c r="F22" s="30" t="n"/>
       <c r="G22" s="30" t="n">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
@@ -967,7 +967,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2286,6 +2286,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>18997.3</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2302,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2402,7 +2421,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,C2)+1)/2)/COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$38,D2,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$38,D2,$C$2:$C$38,C2)+1)/2)/COUNTIFS($D$2:$D$38,D2,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2444,7 +2463,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,C3)+1)/2)/COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$38,D3,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$38,D3,$C$2:$C$38,C3)+1)/2)/COUNTIFS($D$2:$D$38,D3,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2486,7 +2505,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,C4)+1)/2)/COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$38,D4,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$38,D4,$C$2:$C$38,C4)+1)/2)/COUNTIFS($D$2:$D$38,D4,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2528,7 +2547,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,C5)+1)/2)/COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$38,D5,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$38,D5,$C$2:$C$38,C5)+1)/2)/COUNTIFS($D$2:$D$38,D5,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2573,7 +2592,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,C6)+1)/2)/COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$38,D6,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$38,D6,$C$2:$C$38,C6)+1)/2)/COUNTIFS($D$2:$D$38,D6,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2618,7 +2637,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,C7)+1)/2)/COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$38,D7,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$38,D7,$C$2:$C$38,C7)+1)/2)/COUNTIFS($D$2:$D$38,D7,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2663,7 +2682,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,C8)+1)/2)/COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$38,D8,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$38,D8,$C$2:$C$38,C8)+1)/2)/COUNTIFS($D$2:$D$38,D8,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2708,7 +2727,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,C9)+1)/2)/COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$38,D9,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$38,D9,$C$2:$C$38,C9)+1)/2)/COUNTIFS($D$2:$D$38,D9,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2753,7 +2772,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,C10)+1)/2)/COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$38,D10,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$38,D10,$C$2:$C$38,C10)+1)/2)/COUNTIFS($D$2:$D$38,D10,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2798,7 +2817,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,C11)+1)/2)/COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$38,D11,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$38,D11,$C$2:$C$38,C11)+1)/2)/COUNTIFS($D$2:$D$38,D11,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2843,7 +2862,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,C12)+1)/2)/COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$38,D12,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$38,D12,$C$2:$C$38,C12)+1)/2)/COUNTIFS($D$2:$D$38,D12,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2888,7 +2907,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,C13)+1)/2)/COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$38,D13,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$38,D13,$C$2:$C$38,C13)+1)/2)/COUNTIFS($D$2:$D$38,D13,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2933,7 +2952,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,C14)+1)/2)/COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$38,D14,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$38,D14,$C$2:$C$38,C14)+1)/2)/COUNTIFS($D$2:$D$38,D14,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2978,7 +2997,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,C15)+1)/2)/COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$38,D15,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$38,D15,$C$2:$C$38,C15)+1)/2)/COUNTIFS($D$2:$D$38,D15,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3023,7 +3042,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,C16)+1)/2)/COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$38,D16,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$38,D16,$C$2:$C$38,C16)+1)/2)/COUNTIFS($D$2:$D$38,D16,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3068,7 +3087,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,C17)+1)/2)/COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$38,D17,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$38,D17,$C$2:$C$38,C17)+1)/2)/COUNTIFS($D$2:$D$38,D17,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3113,7 +3132,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,C18)+1)/2)/COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$38,D18,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$38,D18,$C$2:$C$38,C18)+1)/2)/COUNTIFS($D$2:$D$38,D18,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3128,7 +3147,10 @@
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="30" t="n"/>
+      <c r="K18" s="30">
+        <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
@@ -3155,7 +3177,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,C19)+1)/2)/COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$38,D19,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$38,D19,$C$2:$C$38,C19)+1)/2)/COUNTIFS($D$2:$D$38,D19,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3197,7 +3219,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,C20)+1)/2)/COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$38,D20,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$38,D20,$C$2:$C$38,C20)+1)/2)/COUNTIFS($D$2:$D$38,D20,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3239,7 +3261,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,C21)+1)/2)/COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$38,D21,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$38,D21,$C$2:$C$38,C21)+1)/2)/COUNTIFS($D$2:$D$38,D21,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3281,7 +3303,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,C22)+1)/2)/COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$38,D22,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$38,D22,$C$2:$C$38,C22)+1)/2)/COUNTIFS($D$2:$D$38,D22,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3323,7 +3345,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,C23)+1)/2)/COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$38,D23,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$38,D23,$C$2:$C$38,C23)+1)/2)/COUNTIFS($D$2:$D$38,D23,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3365,7 +3387,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,C24)+1)/2)/COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$38,D24,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$38,D24,$C$2:$C$38,C24)+1)/2)/COUNTIFS($D$2:$D$38,D24,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3407,7 +3429,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,C25)+1)/2)/COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$38,D25,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$38,D25,$C$2:$C$38,C25)+1)/2)/COUNTIFS($D$2:$D$38,D25,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3449,7 +3471,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,C26)+1)/2)/COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$38,D26,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$38,D26,$C$2:$C$38,C26)+1)/2)/COUNTIFS($D$2:$D$38,D26,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3460,7 +3482,10 @@
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="30" t="n"/>
+      <c r="J26" s="30">
+        <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K26" s="30" t="n"/>
       <c r="L26" s="30" t="n"/>
     </row>
@@ -3488,7 +3513,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,C27)+1)/2)/COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$38,D27,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$38,D27,$C$2:$C$38,C27)+1)/2)/COUNTIFS($D$2:$D$38,D27,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3527,7 +3552,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,C28)+1)/2)/COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$38,D28,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$38,D28,$C$2:$C$38,C28)+1)/2)/COUNTIFS($D$2:$D$38,D28,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3566,7 +3591,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,C29)+1)/2)/COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$38,D29,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$38,D29,$C$2:$C$38,C29)+1)/2)/COUNTIFS($D$2:$D$38,D29,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3605,7 +3630,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,C30)+1)/2)/COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$38,D30,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$38,D30,$C$2:$C$38,C30)+1)/2)/COUNTIFS($D$2:$D$38,D30,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3644,7 +3669,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,C31)+1)/2)/COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$38,D31,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$38,D31,$C$2:$C$38,C31)+1)/2)/COUNTIFS($D$2:$D$38,D31,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3683,7 +3708,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,C32)+1)/2)/COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$38,D32,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$38,D32,$C$2:$C$38,C32)+1)/2)/COUNTIFS($D$2:$D$38,D32,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3722,7 +3747,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,C33)+1)/2)/COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$38,D33,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$38,D33,$C$2:$C$38,C33)+1)/2)/COUNTIFS($D$2:$D$38,D33,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3761,14 +3786,17 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,C34)+1)/2)/COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$38,D34,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$38,D34,$C$2:$C$38,C34)+1)/2)/COUNTIFS($D$2:$D$38,D34,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="30" t="n"/>
+      <c r="I34" s="30">
+        <f>IFERROR(B38/B34-1,"")</f>
+        <v/>
+      </c>
       <c r="J34" s="30" t="n"/>
       <c r="K34" s="30" t="n"/>
       <c r="L34" s="30" t="n"/>
@@ -3797,7 +3825,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,C35)+1)/2)/COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$38,D35,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$38,D35,$C$2:$C$38,C35)+1)/2)/COUNTIFS($D$2:$D$38,D35,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3833,7 +3861,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,C36)+1)/2)/COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$38,D36,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$38,D36,$C$2:$C$38,C36)+1)/2)/COUNTIFS($D$2:$D$38,D36,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3869,7 +3897,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,C37)+1)/2)/COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$38,D37,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$38,D37,$C$2:$C$38,C37)+1)/2)/COUNTIFS($D$2:$D$38,D37,$C$2:$C$38,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3880,6 +3908,42 @@
       <c r="J37" s="30" t="n"/>
       <c r="K37" s="30" t="n"/>
       <c r="L37" s="30" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B38" s="24" t="n">
+        <v>18997.3</v>
+      </c>
+      <c r="C38" s="25" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E38" s="33">
+        <f>IFERROR(B38/C38,"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="30">
+        <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="30">
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$38,D38,$C$2:$C$38,"&gt;0",$C$2:$C$38,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$38,D38,$C$2:$C$38,C38)+1)/2)/COUNTIFS($D$2:$D$38,D38,$C$2:$C$38,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H38">
+        <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I38" s="30" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3894,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3902,7 +3966,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4216,6 +4280,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>18997.3</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.10447761194</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.422392832274</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4256,7 +4353,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18997.3</v>
+        <v>18721.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.71</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1044776119402985</v>
+        <v>0.09701492537313433</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1209.248886059834</v>
+        <v>1209.37015503876</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4223928322741297</v>
+        <v>0.4221652951595576</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06365372374283895</v>
+        <v>0.06459948320413436</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>89.55223880597015</v>
+        <v>90.29850746268657</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>92.68656716417911</v>
+        <v>93.20895522388059</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23969.04042011457</v>
+        <v>23971.44414451827</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2617077384741291</v>
+        <v>0.2804540420819488</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29455.57536600891</v>
+        <v>29458.52930509413</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5505137764844958</v>
+        <v>0.5735511258767072</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4313,6 +4313,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>18721.05</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.42216529516</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4353,7 +4386,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18721.05</v>
+        <v>18830.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.48</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1209.37015503876</v>
+        <v>1209.402697495183</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4221652951595576</v>
+        <v>0.4225792679619784</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06459948320413436</v>
+        <v>0.06422607578676942</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23971.44414451827</v>
+        <v>23972.0891824938</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2804540420819488</v>
+        <v>0.2730525736306082</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29458.52930509413</v>
+        <v>29459.32199284338</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5735511258767072</v>
+        <v>0.5644554546288651</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4346,6 +4346,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>18830.4</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.422579267962</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4386,7 +4419,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18830.4</v>
+        <v>18908</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.57</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1209.402697495183</v>
+        <v>1208.951406649616</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4225792679619784</v>
+        <v>0.4215889560278727</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06422607578676942</v>
+        <v>0.06393861892583121</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23972.0891824938</v>
+        <v>23963.14395323346</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2730525736306082</v>
+        <v>0.2673547679941539</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29459.32199284338</v>
+        <v>29448.32919254658</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5644554546288651</v>
+        <v>0.5574534161490683</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4379,6 +4379,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>18908</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.421588956028</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4419,7 +4452,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18908</v>
+        <v>18736.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.64</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1208.951406649616</v>
+        <v>1208.81935483871</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4215889560278727</v>
+        <v>0.4214578446627495</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06393861892583121</v>
+        <v>0.06451612903225806</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23963.14395323346</v>
+        <v>23960.52649769585</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2673547679941539</v>
+        <v>0.2788018433179722</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29448.32919254658</v>
+        <v>29445.11259907834</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5574534161490683</v>
+        <v>0.5715207373271889</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4412,6 +4412,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>18736.7</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.421457844663</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4452,7 +4485,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18736.7</v>
+        <v>18393.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.5</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1208.81935483871</v>
+        <v>1209.289940828402</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4214578446627495</v>
+        <v>0.4222931993936085</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.06574621959237344</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23960.52649769585</v>
+        <v>23969.85418427726</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2788018433179722</v>
+        <v>0.3031839954916877</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29445.11259907834</v>
+        <v>29456.57540152155</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5715207373271889</v>
+        <v>0.6014839860993706</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4445,6 +4445,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>18393.3</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.422293199394</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4485,7 +4518,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18393.3</v>
+        <v>18675.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.21</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1209.289940828402</v>
+        <v>1209.540155440415</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4222931993936085</v>
+        <v>0.4226201287603655</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06574621959237344</v>
+        <v>0.06476683937823835</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23969.85418427726</v>
+        <v>23974.81379533678</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3031839954916877</v>
+        <v>0.2837712805329384</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29456.57540152155</v>
+        <v>29462.67027202073</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6014839860993706</v>
+        <v>0.5776276831976317</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4478,6 +4478,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>18675.3</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.42262012876</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4518,7 +4551,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18675.3</v>
+        <v>18594.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.44</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1209.540155440415</v>
+        <v>1210.608723958333</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4226201287603655</v>
+        <v>0.4235318885362731</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06476683937823835</v>
+        <v>0.06510416666666667</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23974.81379533678</v>
+        <v>23995.99434988839</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2837712805329384</v>
+        <v>0.2904575892857144</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29462.67027202073</v>
+        <v>29488.69907459078</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5776276831976317</v>
+        <v>0.5858444940476193</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4511,6 +4511,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>18594.95</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.423531888536</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4551,7 +4584,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18594.95</v>
+        <v>18805.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.36</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1210.608723958333</v>
+        <v>1210.885383129427</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4235318885362731</v>
+        <v>0.4240804818641333</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06510416666666667</v>
+        <v>0.06439150032195751</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23995.99434988839</v>
+        <v>24001.47812988685</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2904575892857144</v>
+        <v>0.2763315242388003</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29488.69907459078</v>
+        <v>29495.43809677123</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5858444940476193</v>
+        <v>0.5684849599852821</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4544,6 +4544,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>18805.05</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.424080481864</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4584,7 +4617,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18805.05</v>
+        <v>18810.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.53</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1210.885383129427</v>
+        <v>1210.437580437581</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4240804818641333</v>
+        <v>0.4232666020006628</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06439150032195751</v>
+        <v>0.06435006435006435</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24001.47812988685</v>
+        <v>23992.60204081633</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2763315242388003</v>
+        <v>0.2755102040816326</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29495.43809677123</v>
+        <v>29484.53026291599</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5684849599852821</v>
+        <v>0.5674756389042106</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4577,6 +4577,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>18810.2</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.423266602001</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4617,7 +4650,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18810.2</v>
+        <v>18854.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.54</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1210.437580437581</v>
+        <v>1210.960179833012</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4232666020006628</v>
+        <v>0.4242127229509098</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06435006435006435</v>
+        <v>0.06422607578676942</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23992.60204081633</v>
+        <v>24002.96070740435</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2755102040816326</v>
+        <v>0.2730525736306082</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29484.53026291599</v>
+        <v>29497.26003761813</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5674756389042106</v>
+        <v>0.5644554546288651</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4610,6 +4610,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>18854.65</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.424212722951</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4650,7 +4683,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18854.65</v>
+        <v>18867.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1210.960179833012</v>
+        <v>1211.759794476557</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4242127229509098</v>
+        <v>0.4239211861856518</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24002.96070740435</v>
+        <v>24018.81021194605</v>
       </c>
       <c r="D13" s="30" t="n">
         <v>0.2730525736306082</v>
@@ -755,7 +755,7 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29497.26003761813</v>
+        <v>29516.73750802826</v>
       </c>
       <c r="D14" s="30" t="n">
         <v>0.5644554546288651</v>
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4643,6 +4643,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>18867.1</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.423921186186</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4683,7 +4716,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18867.1</v>
+        <v>18756.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.57</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1211.759794476557</v>
+        <v>1217.938311688312</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4239211861856518</v>
+        <v>0.4307325255470977</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06422607578676942</v>
+        <v>0.06493506493506493</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24018.81021194605</v>
+        <v>24141.27724953618</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2730525736306082</v>
+        <v>0.2871057513914654</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29516.73750802826</v>
+        <v>29667.23736085343</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5644554546288651</v>
+        <v>0.5817254174397031</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4676,6 +4676,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>18756.25</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.430732525547</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4716,7 +4749,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18756.25</v>
+        <v>18635.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1217.938311688312</v>
+        <v>1217.977124183006</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4307325255470977</v>
+        <v>0.4288799138725023</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06493506493506493</v>
+        <v>0.06535947712418301</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24141.27724953618</v>
+        <v>24142.04656862745</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2871057513914654</v>
+        <v>0.295518207282913</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29667.23736085343</v>
+        <v>29668.18277777778</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5817254174397031</v>
+        <v>0.5920634920634922</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4709,6 +4709,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>18635.05</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.428879913873</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4749,7 +4782,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18635.05</v>
+        <v>18584.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.3</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1217.977124183006</v>
+        <v>1228.341044282882</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4288799138725023</v>
+        <v>0.4410384322598033</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06535947712418301</v>
+        <v>0.06609385327164573</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24142.04656862745</v>
+        <v>24347.47427060711</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.295518207282913</v>
+        <v>0.3100745916344063</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29668.18277777778</v>
+        <v>29920.63306581059</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5920634920634922</v>
+        <v>0.609951845906902</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4742,6 +4742,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>18584.8</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.44103843226</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4782,7 +4815,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18584.8</v>
+        <v>18369.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.13</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.09701492537313433</v>
+        <v>0.08208955223880597</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1228.341044282882</v>
+        <v>1228.739130434783</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4410384322598033</v>
+        <v>0.4413785433333424</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06609385327164573</v>
+        <v>0.06688963210702341</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>90.29850746268657</v>
+        <v>91.79104477611941</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.20895522388059</v>
+        <v>94.25373134328358</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24347.47427060711</v>
+        <v>24355.3649068323</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3100745916344063</v>
+        <v>0.3258480649784998</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29920.63306581059</v>
+        <v>29930.3298757764</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.609951845906902</v>
+        <v>0.6293358815097947</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4775,6 +4775,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>18369.65</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.0820895522388</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.441378543333</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4815,7 +4848,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18369.65</v>
+        <v>18560.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>14.95</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08208955223880597</v>
+        <v>0.09701492537313433</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1228.739130434783</v>
+        <v>1228.378557246856</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4413785433333424</v>
+        <v>0.4418262347635751</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06688963210702341</v>
+        <v>0.06618133686300463</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.79104477611941</v>
+        <v>90.29850746268657</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>94.25373134328358</v>
+        <v>93.20895522388059</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24355.3649068323</v>
+        <v>24348.21783114304</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3258480649784998</v>
+        <v>0.3118086413916989</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29930.3298757764</v>
+        <v>29921.54682802307</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6293358815097947</v>
+        <v>0.6120828212158458</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4808,6 +4808,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>18560.8</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.441826234764</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4848,7 +4881,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18560.8</v>
+        <v>18593</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.11</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1228.378557246856</v>
+        <v>1226.451187335092</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4418262347635751</v>
+        <v>0.439581350527285</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06618133686300463</v>
+        <v>0.06596306068601583</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24348.21783114304</v>
+        <v>24310.01460610629</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3118086413916989</v>
+        <v>0.3074820957406708</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29921.54682802307</v>
+        <v>29874.59885035808</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6120828212158458</v>
+        <v>0.6067659253675084</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4841,6 +4841,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>18593</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.439581350527</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4881,7 +4914,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18593</v>
+        <v>18616.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.16</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1226.451187335092</v>
+        <v>1225.599078341014</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.439581350527285</v>
+        <v>0.4385176503358508</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06596306068601583</v>
+        <v>0.06583278472679395</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24310.01460610629</v>
+        <v>24293.1245885451</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3074820957406708</v>
+        <v>0.30489984012038</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29874.59885035808</v>
+        <v>29853.8426925609</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6067659253675084</v>
+        <v>0.6035925891093767</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4874,6 +4874,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>18616.85</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.438517650336</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4914,7 +4947,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18616.85</v>
+        <v>18750.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.19</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1225.599078341014</v>
+        <v>1225.549019607843</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4385176503358508</v>
+        <v>0.4384011002643611</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06583278472679395</v>
+        <v>0.06535947712418301</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24293.1245885451</v>
+        <v>24292.13235294117</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.30489984012038</v>
+        <v>0.295518207282913</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29853.8426925609</v>
+        <v>29852.62333333333</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6035925891093767</v>
+        <v>0.592063492063492</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4907,6 +4907,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>18750.9</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.438401100264</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4947,7 +4980,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
+++ b/docs/downloads/indices/nifty-alpha-quality-value-low-volatility-30.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>18750.9</v>
+        <v>18779.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>15.3</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1225.549019607843</v>
+        <v>1229.011780104712</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.4384011002643611</v>
+        <v>0.4424252911910129</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.06535947712418301</v>
+        <v>0.06544502617801047</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.82142857142857</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24292.13235294117</v>
+        <v>24360.76921278982</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.295518207282913</v>
+        <v>0.2972139117427073</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.35857142857143</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>29852.62333333333</v>
+        <v>29936.97123223635</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.592063492063492</v>
+        <v>0.5941473448017953</v>
       </c>
     </row>
     <row r="16">
@@ -3958,7 +3958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4940,6 +4940,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>18779.3</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.442425291191</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4980,7 +5013,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
